--- a/Assets/Data/Map0020.xlsx
+++ b/Assets/Data/Map0020.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE99306-DB23-4CB2-A967-F2CB8C98C9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Map" sheetId="1" r:id="rId1"/>
@@ -19,18 +13,7 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -38,39 +21,30 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="16">
   <si>
     <t>_</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Id</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>StageId</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>InitX</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>InitY</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>UnitType</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>*</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>InitTeamId</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Rate</t>
@@ -89,18 +63,22 @@
   </si>
   <si>
     <t>MoveType</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>MoveParam</t>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,27 +90,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -140,9 +440,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -157,28 +699,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Stages"/>
       <sheetName val="StageEvents"/>
@@ -596,22 +1179,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AO41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="2.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="40" width="3.26953125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="2.81640625" customWidth="1"/>
+    <col min="1" max="1" width="3.27272727272727" customWidth="1"/>
+    <col min="2" max="10" width="2.27272727272727" customWidth="1"/>
+    <col min="11" max="40" width="3.27272727272727" customWidth="1"/>
+    <col min="41" max="41" width="2.81818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:41">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -736,7 +1319,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:41">
       <c r="A2">
         <v>1</v>
       </c>
@@ -861,7 +1444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:41">
       <c r="A3">
         <v>2</v>
       </c>
@@ -986,7 +1569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:41">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1111,7 +1694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1236,7 +1819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1361,7 +1944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1486,7 +2069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1611,7 +2194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1736,7 +2319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1861,7 +2444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1986,7 +2569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2111,7 +2694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2236,7 +2819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2361,7 +2944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2486,7 +3069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2611,7 +3194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:41">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2736,7 +3319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:41">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2861,7 +3444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:41">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2986,7 +3569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:41">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3111,7 +3694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:41">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3236,7 +3819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:41">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3361,7 +3944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:41">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3486,7 +4069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:41">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3611,7 +4194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:41">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3736,7 +4319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:41">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3861,7 +4444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:41">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3986,7 +4569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:41">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4111,7 +4694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:41">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4236,7 +4819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:41">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4361,7 +4944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:41">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4486,7 +5069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:41">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4611,7 +5194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:41">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4736,7 +5319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:41">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4857,7 +5440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:41">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4978,7 +5561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:41">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5089,7 +5672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:41">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5196,7 +5779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:41">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5301,7 +5884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:41">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5410,7 +5993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:41">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5529,7 +6112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:41">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5655,18 +6238,19 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30ECAC24-1D32-444C-8B2B-B82C8B7A4C87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="7"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -5710,7 +6294,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>2010</v>
       </c>
@@ -5755,7 +6339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>2020</v>
       </c>
@@ -5800,7 +6384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>2030</v>
       </c>
@@ -5845,7 +6429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>2040</v>
       </c>
@@ -5890,7 +6474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>2050</v>
       </c>
@@ -5935,7 +6519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>2060</v>
       </c>
@@ -5980,7 +6564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>2070</v>
       </c>
@@ -6026,7 +6610,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/Map0020.xlsx
+++ b/Assets/Data/Map0020.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="16">
   <si>
     <t>_</t>
   </si>
@@ -73,10 +73,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -94,30 +94,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -131,9 +124,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -156,23 +172,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,39 +192,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,8 +207,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,7 +247,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -259,7 +277,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -271,7 +301,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -283,25 +355,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -319,115 +427,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,8 +459,38 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -469,7 +499,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -491,50 +521,20 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -546,145 +546,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1383,9 +1383,7 @@
       <c r="U2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="V2" s="2"/>
       <c r="W2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1508,9 +1506,7 @@
       <c r="U3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="V3" s="2"/>
       <c r="W3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1633,9 +1629,7 @@
       <c r="U4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="V4" s="2"/>
       <c r="W4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1755,15 +1749,9 @@
       <c r="T5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="U5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
       <c r="X5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1880,15 +1868,9 @@
       <c r="T6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="U6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
       <c r="X6" s="2" t="s">
         <v>1</v>
       </c>
@@ -2008,9 +1990,7 @@
       <c r="U7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="V7" s="2"/>
       <c r="W7" s="2" t="s">
         <v>1</v>
       </c>
@@ -5374,8 +5354,12 @@
       <c r="R34" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2"/>
+      <c r="S34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="U34" s="2" t="s">
         <v>1</v>
       </c>
@@ -5498,8 +5482,12 @@
       <c r="S35" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="T35" s="2"/>
-      <c r="U35" s="2"/>
+      <c r="T35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="V35" s="2" t="s">
         <v>1</v>
       </c>
@@ -5619,19 +5607,33 @@
       <c r="S36" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="T36" s="2"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="2"/>
-      <c r="W36" s="2"/>
-      <c r="X36" s="2"/>
+      <c r="T36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="Y36" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="Z36" s="2"/>
+      <c r="Z36" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AA36" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AB36" s="2"/>
+      <c r="AB36" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AC36" s="2" t="s">
         <v>1</v>
       </c>
@@ -5736,15 +5738,33 @@
       <c r="U37" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="V37" s="2"/>
-      <c r="W37" s="2"/>
-      <c r="X37" s="2"/>
-      <c r="Y37" s="2"/>
-      <c r="Z37" s="2"/>
-      <c r="AA37" s="2"/>
-      <c r="AB37" s="2"/>
-      <c r="AC37" s="2"/>
-      <c r="AD37" s="2"/>
+      <c r="V37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD37" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AE37" s="2" t="s">
         <v>1</v>
       </c>
@@ -5846,16 +5866,36 @@
       <c r="V38" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="W38" s="2"/>
-      <c r="X38" s="2"/>
-      <c r="Y38" s="2"/>
-      <c r="Z38" s="2"/>
-      <c r="AA38" s="2"/>
-      <c r="AB38" s="2"/>
-      <c r="AC38" s="2"/>
-      <c r="AD38" s="2"/>
-      <c r="AE38" s="2"/>
-      <c r="AF38" s="2"/>
+      <c r="W38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AG38" s="2" t="s">
         <v>1</v>
       </c>
@@ -5975,14 +6015,30 @@
       <c r="AD39" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AE39" s="2"/>
-      <c r="AF39" s="2"/>
-      <c r="AG39" s="2"/>
-      <c r="AH39" s="2"/>
-      <c r="AI39" s="2"/>
-      <c r="AJ39" s="2"/>
-      <c r="AK39" s="2"/>
-      <c r="AL39" s="2"/>
+      <c r="AE39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK39" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL39" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AM39" s="2" t="s">
         <v>1</v>
       </c>
@@ -6090,15 +6146,21 @@
       <c r="AF40" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AG40" s="2"/>
+      <c r="AG40" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AH40" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AI40" s="2"/>
+      <c r="AI40" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AJ40" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AK40" s="2"/>
+      <c r="AK40" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="AL40" s="2" t="s">
         <v>1</v>
       </c>
@@ -6247,8 +6309,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="7"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="3"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
@@ -6305,35 +6367,35 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="F2" t="str">
         <f>INDEX([1]Define!L:L,MATCH(E2,[1]Define!K:K))</f>
-        <v>Battler</v>
+        <v>Basement</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
       <c r="I2">
-        <v>1101</v>
+        <v>1</v>
       </c>
       <c r="J2">
+        <v>30</v>
+      </c>
+      <c r="K2">
         <v>0</v>
-      </c>
-      <c r="K2">
-        <v>1011</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -6347,20 +6409,20 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F3" t="str">
         <f>INDEX([1]Define!L:L,MATCH(E3,[1]Define!K:K))</f>
-        <v>Basement</v>
+        <v>SelectActor</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>100</v>
@@ -6372,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -6392,220 +6454,40 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="F4" t="str">
         <f>INDEX([1]Define!L:L,MATCH(E4,[1]Define!K:K))</f>
-        <v>Battler</v>
+        <v>SelectActor</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
       <c r="I4">
-        <v>1031</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1011</v>
+        <v>1000</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5">
-        <v>2040</v>
-      </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>24</v>
-      </c>
-      <c r="D5">
-        <v>37</v>
-      </c>
-      <c r="E5">
-        <v>1000</v>
-      </c>
-      <c r="F5" t="str">
-        <f>INDEX([1]Define!L:L,MATCH(E5,[1]Define!K:K))</f>
-        <v>Battler</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
-      <c r="I5">
-        <v>1041</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>1011</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>10</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6">
-        <v>2050</v>
-      </c>
-      <c r="B6">
-        <v>20</v>
-      </c>
-      <c r="C6">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>36</v>
-      </c>
-      <c r="E6">
-        <v>1000</v>
-      </c>
-      <c r="F6" t="str">
-        <f>INDEX([1]Define!L:L,MATCH(E6,[1]Define!K:K))</f>
-        <v>Battler</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
-      <c r="I6">
-        <v>1051</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>1011</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7">
-        <v>2060</v>
-      </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>35</v>
-      </c>
-      <c r="E7">
-        <v>1000</v>
-      </c>
-      <c r="F7" t="str">
-        <f>INDEX([1]Define!L:L,MATCH(E7,[1]Define!K:K))</f>
-        <v>Battler</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>100</v>
-      </c>
-      <c r="I7">
-        <v>1061</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>1011</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>20</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8">
-        <v>2070</v>
-      </c>
-      <c r="B8">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>21</v>
-      </c>
-      <c r="D8">
-        <v>36</v>
-      </c>
-      <c r="E8">
-        <v>1000</v>
-      </c>
-      <c r="F8" t="str">
-        <f>INDEX([1]Define!L:L,MATCH(E8,[1]Define!K:K))</f>
-        <v>Battler</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
-        <v>100</v>
-      </c>
-      <c r="I8">
-        <v>1071</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>1011</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8">
         <v>0</v>
       </c>
     </row>
